--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484545_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484545_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0195</v>
+        <v>9.044499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3584</v>
+        <v>7.2596</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6611</v>
+        <v>1.7849</v>
       </c>
       <c r="G2" t="n">
         <v>5.8954</v>
@@ -610,13 +610,13 @@
         <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0245</v>
+        <v>1.0496</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2338</v>
+        <v>1.135</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2093</v>
+        <v>-0.0854</v>
       </c>
       <c r="V2" t="n">
         <v>0.6335</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5025</v>
+        <v>5.5328</v>
       </c>
       <c r="E3" t="n">
-        <v>4.639</v>
+        <v>4.694</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8635</v>
+        <v>0.8388</v>
       </c>
       <c r="G3" t="n">
         <v>3.8878</v>
@@ -688,13 +688,13 @@
         <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4011</v>
+        <v>-0.3709</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2398</v>
+        <v>-0.1847</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1613</v>
+        <v>-0.1861</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SAEZ GONZALEZ</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4425</v>
+        <v>4.9235</v>
       </c>
       <c r="E4" t="n">
-        <v>3.218</v>
+        <v>5.689</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2246</v>
+        <v>-0.7655</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7125</v>
+        <v>6.2545</v>
       </c>
       <c r="H4" t="n">
-        <v>1.674</v>
+        <v>2.1545</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0385</v>
+        <v>4.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9555</v>
+        <v>6.6441</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8206</v>
+        <v>2.576</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1349</v>
+        <v>4.0682</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.243</v>
+        <v>-0.3896</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1466</v>
+        <v>-0.4214</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0964</v>
+        <v>0.0318</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1833</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R4" t="n">
         <v>1.0995</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5468</v>
+        <v>-0.3152</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1787</v>
+        <v>0.2048</v>
       </c>
       <c r="U4" t="n">
-        <v>0.368</v>
+        <v>-0.52</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.1517</v>
+        <v>4.1011</v>
       </c>
       <c r="E5" t="n">
-        <v>4.7685</v>
+        <v>2.9687</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6169</v>
+        <v>1.1324</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2545</v>
+        <v>4.6239</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1545</v>
+        <v>3.5435</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>1.0803</v>
       </c>
       <c r="J5" t="n">
-        <v>6.6441</v>
+        <v>4.6272</v>
       </c>
       <c r="K5" t="n">
-        <v>2.576</v>
+        <v>3.8672</v>
       </c>
       <c r="L5" t="n">
-        <v>4.0682</v>
+        <v>0.76</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3896</v>
+        <v>-0.0033</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4214</v>
+        <v>-0.3237</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0318</v>
+        <v>0.3204</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6493</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.087</v>
+        <v>1.1003</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7157</v>
+        <v>0.1637</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3714</v>
+        <v>0.9366</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6335</v>
+        <v>-1.2566</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5889</v>
+        <v>0.0104</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>J. SAEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9705</v>
+        <v>3.4399</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1444</v>
+        <v>2.2153</v>
       </c>
       <c r="F6" t="n">
-        <v>1.826</v>
+        <v>1.2246</v>
       </c>
       <c r="G6" t="n">
-        <v>4.6239</v>
+        <v>1.7125</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5435</v>
+        <v>1.674</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0803</v>
+        <v>0.0385</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6272</v>
+        <v>1.9555</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8672</v>
+        <v>1.8206</v>
       </c>
       <c r="L6" t="n">
-        <v>0.76</v>
+        <v>0.1349</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0033</v>
+        <v>-0.243</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3237</v>
+        <v>-0.1466</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3204</v>
+        <v>-0.0964</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4661</v>
+        <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9697</v>
+        <v>1.5441</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6606</v>
+        <v>1.1761</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6303</v>
+        <v>0.368</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2566</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>P. FERRI BARCENAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.883</v>
+        <v>3.3256</v>
       </c>
       <c r="E7" t="n">
-        <v>0.746</v>
+        <v>3.1756</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1369</v>
+        <v>0.15</v>
       </c>
       <c r="G7" t="n">
-        <v>2.8881</v>
+        <v>4.4711</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3145</v>
+        <v>1.7012</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2026</v>
+        <v>2.7699</v>
       </c>
       <c r="J7" t="n">
-        <v>3.238</v>
+        <v>5.4453</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4519</v>
+        <v>2.0341</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7861</v>
+        <v>3.4112</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3499</v>
+        <v>-0.9742</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7664</v>
+        <v>-0.3329</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4164</v>
+        <v>-0.6413</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0995</v>
+        <v>-0.733</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5656</v>
+        <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0736</v>
+        <v>0.2106</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1524</v>
+        <v>0.1859</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0788</v>
+        <v>0.0247</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0208</v>
+        <v>-0.6231</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0208</v>
+        <v>-0.6231</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. FERRI BARCENAS</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8201</v>
+        <v>2.8037</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6948</v>
+        <v>0.5677</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1252</v>
+        <v>2.236</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4711</v>
+        <v>2.8881</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7012</v>
+        <v>-0.3145</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7699</v>
+        <v>3.2026</v>
       </c>
       <c r="J8" t="n">
-        <v>5.4453</v>
+        <v>3.238</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0341</v>
+        <v>0.4519</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4112</v>
+        <v>2.7861</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9742</v>
+        <v>-0.3499</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3329</v>
+        <v>-0.7664</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6413</v>
+        <v>0.4164</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.733</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0995</v>
+        <v>2.5656</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2949</v>
+        <v>0.9943</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2949</v>
+        <v>0.974</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0001</v>
+        <v>0.0203</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6231</v>
+        <v>0.0208</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6231</v>
+        <v>0.0208</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.632</v>
+        <v>0.3083</v>
       </c>
       <c r="E9" t="n">
-        <v>1.6521</v>
+        <v>1.1303</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0201</v>
+        <v>-0.822</v>
       </c>
       <c r="G9" t="n">
         <v>1.1182</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7362</v>
+        <v>0.4125</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1169</v>
+        <v>0.595</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3807</v>
+        <v>-0.1825</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5889</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>J. VERGARA APARICIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5314</v>
+        <v>0.3004</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.963</v>
+        <v>-0.3441</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4317</v>
+        <v>0.6445</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3991</v>
+        <v>-2.1063</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0272</v>
+        <v>-1.4812</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4263</v>
+        <v>-0.6251</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0633</v>
+        <v>-2.1823</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0217</v>
+        <v>-1.1087</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0417</v>
+        <v>-1.0737</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3357</v>
+        <v>0.076</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0489</v>
+        <v>-0.3726</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3846</v>
+        <v>0.4486</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0142</v>
+        <v>0.1056</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1101</v>
+        <v>0.5713</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0959</v>
+        <v>-0.4657</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.5681</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. VERGARA APARICIO</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5823</v>
+        <v>-0.3886</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8799</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2976</v>
+        <v>0.3821</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1063</v>
+        <v>0.3991</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4812</v>
+        <v>-0.0272</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6251</v>
+        <v>0.4263</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1823</v>
+        <v>0.0633</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1087</v>
+        <v>0.0217</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0737</v>
+        <v>0.0417</v>
       </c>
       <c r="M11" t="n">
-        <v>0.076</v>
+        <v>0.3357</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3726</v>
+        <v>-0.0489</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4486</v>
+        <v>0.3846</v>
       </c>
       <c r="P11" t="n">
-        <v>0.733</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7771</v>
+        <v>0.1286</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0355</v>
+        <v>0.0822</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8125</v>
+        <v>0.0464</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5681</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7043</v>
+        <v>-1.1378</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1628</v>
+        <v>0.5063</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8671</v>
+        <v>-1.6441</v>
       </c>
       <c r="G12" t="n">
         <v>0.1394</v>
@@ -1390,13 +1390,13 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2993</v>
+        <v>-0.7328</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6606</v>
+        <v>-0.3171</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6387</v>
+        <v>-0.4157</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2774</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0684</v>
+        <v>-4.1675</v>
       </c>
       <c r="E13" t="n">
         <v>-4.5031</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4347</v>
+        <v>0.3356</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7852</v>
@@ -1468,13 +1468,13 @@
         <v>0.1833</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2824</v>
+        <v>0.1833</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0196</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3019</v>
+        <v>0.2029</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>27.53540000000001</v>
+        <v>28.08590000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>22.038</v>
+        <v>22.5886</v>
       </c>
       <c r="F14" t="n">
-        <v>5.4972</v>
+        <v>5.4973</v>
       </c>
       <c r="G14" t="n">
         <v>27.4985</v>
@@ -1519,7 +1519,7 @@
         <v>14.586</v>
       </c>
       <c r="J14" t="n">
-        <v>29.46309999999999</v>
+        <v>29.4631</v>
       </c>
       <c r="K14" t="n">
         <v>16.638</v>
@@ -1546,22 +1546,22 @@
         <v>12.8279</v>
       </c>
       <c r="S14" t="n">
-        <v>3.759600000000002</v>
+        <v>4.31</v>
       </c>
       <c r="T14" t="n">
-        <v>4.016</v>
+        <v>4.566600000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2567000000000001</v>
+        <v>-0.2565000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.8901</v>
+        <v>-1.890100000000001</v>
       </c>
       <c r="W14" t="n">
         <v>3.2194</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.109500000000001</v>
+        <v>-5.1095</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3711</v>
+        <v>0.0412</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7572</v>
+        <v>2.0456</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1283</v>
+        <v>-2.0044</v>
       </c>
       <c r="G15" t="n">
         <v>0.8501</v>
@@ -1624,13 +1624,13 @@
         <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.394</v>
+        <v>0.0183</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3673</v>
+        <v>-0.0788</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0268</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6439</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.761</v>
+        <v>-0.4914</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0899</v>
+        <v>1.186</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8509</v>
+        <v>-1.6774</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1247</v>
@@ -1702,13 +1702,13 @@
         <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6363</v>
+        <v>-0.3667</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1847</v>
+        <v>-0.0886</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4515</v>
+        <v>-0.2781</v>
       </c>
       <c r="V16" t="n">
         <v>0.6335</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1685</v>
+        <v>-1.1991</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.618</v>
+        <v>-1.4257</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4495</v>
+        <v>0.2266</v>
       </c>
       <c r="G17" t="n">
         <v>-2.7168</v>
@@ -1780,13 +1780,13 @@
         <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2367</v>
+        <v>0.2061</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0015</v>
+        <v>0.1908</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2382</v>
+        <v>0.0153</v>
       </c>
       <c r="V17" t="n">
         <v>0.945</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>J. YUBERO OJEDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2613</v>
+        <v>-1.5795</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3322</v>
+        <v>0.0052</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5935</v>
+        <v>-1.5847</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.938</v>
+        <v>-1.5597</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.5465</v>
+        <v>0.7674</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3915</v>
+        <v>-2.3271</v>
       </c>
       <c r="J18" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0157</v>
+        <v>1.8206</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0833</v>
+        <v>-1.1729</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.0056</v>
+        <v>-2.2074</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.5308</v>
+        <v>-1.0532</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4748</v>
+        <v>-1.1541</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2002</v>
+        <v>-0.0094</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9872</v>
+        <v>0.2738</v>
       </c>
       <c r="U18" t="n">
-        <v>0.213</v>
+        <v>-0.2832</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0104</v>
+        <v>-0.0104</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2774</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. YUBERO OJEDA</t>
+          <t>J. MARTINEZ TEJERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6291</v>
+        <v>-1.7717</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0052</v>
+        <v>-0.3383</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6343</v>
+        <v>-1.4334</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5597</v>
+        <v>-2.0913</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7674</v>
+        <v>-0.2513</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.3271</v>
+        <v>-1.84</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6477000000000001</v>
+        <v>-0.3968</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8206</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1729</v>
+        <v>-1.1987</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2074</v>
+        <v>-1.6946</v>
       </c>
       <c r="N19" t="n">
         <v>-1.0532</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1541</v>
+        <v>-0.6413</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9163</v>
+        <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.059</v>
+        <v>-0.6412</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2738</v>
+        <v>0.0585</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3327</v>
+        <v>-0.6997</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0104</v>
+        <v>-0.3219</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0104</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MARTINEZ TEJERO</t>
+          <t>J. GOMEZ MONTES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3268</v>
+        <v>-2.162</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8191000000000001</v>
+        <v>-0.6428</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5077</v>
+        <v>-1.5192</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0913</v>
+        <v>-2.1205</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2513</v>
+        <v>-0.7516</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.84</v>
+        <v>-1.3689</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3968</v>
+        <v>-0.426</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.1734</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1987</v>
+        <v>-0.5994</v>
       </c>
       <c r="M20" t="n">
         <v>-1.6946</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0532</v>
+        <v>-0.925</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6413</v>
+        <v>-0.7695</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1963</v>
+        <v>-1.141</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4223</v>
+        <v>-0.2168</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.774</v>
+        <v>-0.9242</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GONZALEZ SOLER</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5643</v>
+        <v>-2.306</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7818000000000001</v>
+        <v>1.6591</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7825</v>
+        <v>-3.9651</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8128</v>
+        <v>-3.938</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2772</v>
+        <v>-2.5465</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5356</v>
+        <v>-1.3915</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7719</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8394</v>
+        <v>-0.0157</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0674</v>
+        <v>0.0833</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.0409</v>
+        <v>-4.0056</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4379</v>
+        <v>-2.5308</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.603</v>
+        <v>-1.4748</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9266</v>
+        <v>0.1555</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5845</v>
+        <v>0.3141</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3421</v>
+        <v>-0.1586</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3219</v>
+        <v>0.0104</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3219</v>
+        <v>1.2774</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. GOMEZ MONTES</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6923</v>
+        <v>-2.8041</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1235</v>
+        <v>1.5119</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5688</v>
+        <v>-4.316</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1205</v>
+        <v>-3.772</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7516</v>
+        <v>-1.9734</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3689</v>
+        <v>-1.7987</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.426</v>
+        <v>-0.1265</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1734</v>
+        <v>-0.2515</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5994</v>
+        <v>0.125</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6946</v>
+        <v>-3.6456</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.925</v>
+        <v>-1.7219</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7695</v>
+        <v>-1.9237</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0995</v>
+        <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6713</v>
+        <v>-0.5818</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6976</v>
+        <v>0.0208</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9738</v>
+        <v>-0.6026</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>A. GONZALEZ SOLER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7138</v>
+        <v>-3.1937</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8004</v>
+        <v>-1.2626</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5142</v>
+        <v>-1.9312</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.772</v>
+        <v>-3.8128</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9734</v>
+        <v>-2.2772</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7987</v>
+        <v>-1.5356</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1265</v>
+        <v>-0.7719</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2515</v>
+        <v>-0.8394</v>
       </c>
       <c r="L23" t="n">
-        <v>0.125</v>
+        <v>0.0674</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.6456</v>
+        <v>-3.0409</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7219</v>
+        <v>-1.4379</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.9237</v>
+        <v>-1.603</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4915</v>
+        <v>0.2971</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3092</v>
+        <v>0.1037</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8008</v>
+        <v>0.1934</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="W23" t="n">
-        <v>2.5339</v>
+        <v>0.3219</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.9005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6452</v>
+        <v>-3.549</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0865</v>
+        <v>-1.9903</v>
       </c>
       <c r="F24" t="n">
         <v>-1.5587</v>
@@ -2326,10 +2326,10 @@
         <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6787</v>
+        <v>-0.5826</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1666</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U24" t="n">
         <v>-0.5121</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1576</v>
+        <v>-3.7853</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4999</v>
+        <v>-2.8467</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6577</v>
+        <v>-0.9386</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.1228</v>
+        <v>-2.168</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.3148</v>
+        <v>-0.9375</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-1.2305</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1076</v>
+        <v>0.2332</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1333</v>
+        <v>0.8545</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0258</v>
+        <v>-0.6213</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.0152</v>
+        <v>-2.4012</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1815</v>
+        <v>-1.792</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8338</v>
+        <v>-0.6092</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.6493</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2376</v>
+        <v>-0.7743</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6576</v>
+        <v>-0.3311</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4201</v>
+        <v>-0.4433</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6231</v>
+        <v>0.6231</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3011</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3219</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.2443</v>
+        <v>-4.7345</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.2314</v>
+        <v>-3.0768</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0129</v>
+        <v>-1.6577</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.168</v>
+        <v>-2.1228</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9375</v>
+        <v>-1.3148</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.2305</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2332</v>
+        <v>-0.1076</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8545</v>
+        <v>-0.1333</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6213</v>
+        <v>0.0258</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.4012</v>
+        <v>-2.0152</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.792</v>
+        <v>-1.1815</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.6092</v>
+        <v>-0.8338</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.4661</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q26" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.2333</v>
+        <v>-0.3394</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7157</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.4201</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6231</v>
+        <v>-0.6231</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>-0.3011</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6231</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-27.5353</v>
+        <v>-27.5351</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.1753</v>
+        <v>-5.1754</v>
       </c>
       <c r="F27" t="n">
-        <v>-22.36</v>
+        <v>-22.3598</v>
       </c>
       <c r="G27" t="n">
         <v>-27.4984</v>
@@ -2536,10 +2536,10 @@
         <v>1.9645</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7255</v>
+        <v>3.725499999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.761</v>
+        <v>-1.761000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-29.4633</v>
@@ -2560,13 +2560,13 @@
         <v>14.6606</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.759300000000001</v>
+        <v>-3.7594</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2565999999999999</v>
+        <v>0.2566</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.016100000000001</v>
+        <v>-4.0161</v>
       </c>
       <c r="V27" t="n">
         <v>1.89</v>
@@ -2575,7 +2575,7 @@
         <v>5.431300000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>-3.541300000000001</v>
+        <v>-3.5413</v>
       </c>
     </row>
   </sheetData>
